--- a/word-lists/100-wordlist-Polish.xlsx
+++ b/word-lists/100-wordlist-Polish.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A73B165-123B-4ACA-A7A6-20B31C090E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E03605D-E66F-42B1-8142-62600C49E367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{7439BFC4-180C-4C7F-A42F-B8FD52912BDF}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{7659BDD1-C807-4E95-ABD1-C112CF19F6BF}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Polish" sheetId="1" r:id="rId1"/>
@@ -318,16 +318,16 @@
     <t>myśleć</t>
   </si>
   <si>
-    <t>ważny</t>
-  </si>
-  <si>
-    <t>różny</t>
+    <t>zrozumienie</t>
+  </si>
+  <si>
+    <t>różnorodność</t>
   </si>
   <si>
     <t>informacja</t>
   </si>
   <si>
-    <t>rząd</t>
+    <t>zarządzanie</t>
   </si>
   <si>
     <t>pytanie</t>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DFF8DC-D21A-44CE-9BAB-088EB160F80C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C90635-6A2E-4471-B382-C1D39B259484}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2030,7 +2030,7 @@
         <v>77</v>
       </c>
       <c r="C76">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.4">
